--- a/processed_ruby_restored_xlsx/sc111_ノノ１：風呂.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc111_ノノ１：風呂.ss.xlsx
@@ -655,8 +655,8 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Especially Nono-chan's singing — it's fresh to me, and
-I'm captivated by her clear voice.</t>
+          <t>Especially Nono-chan's singing — it's fresh to me,
+and I'm captivated by her clear voice.</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -900,8 +900,8 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>She's wearing a bath towel, but even a single towel is
-a provocative sight.</t>
+          <t>She's wearing a bath towel, but even a single towel
+is a provocative sight.</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1055,7 +1055,8 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>I couldn't help but stare, and Nono-chan scolded me...</t>
+          <t>I couldn't help but stare, and Nono-chan scolded
+me...</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1130,8 +1131,8 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Even though Nono-chan came in on her own, she faltered
-while speaking.</t>
+          <t>Even though Nono-chan came in on her own, she
+faltered while speaking.</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1453,7 +1454,8 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Maybe Nono-chan was startled because she saw me naked.</t>
+          <t>Maybe Nono-chan was startled because she saw me
+naked.</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1529,8 +1531,9 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>「It's obvious you bathe naked, but Nono-chan sometimes
-says things that totally miss the point... ahaha！」</t>
+          <t>「It's obvious you bathe naked, but Nono-chan
+sometimes says things that totally miss the point...
+ahaha！」</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2218,9 +2221,9 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>At the same time as the towel, soft fingertips touched
-my back, and I let out a surprised sound at that
-smooth feeling.</t>
+          <t>At the same time as the towel, soft fingertips
+touched my back, and I let out a surprised sound at
+that smooth feeling.</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2691,9 +2694,9 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan’s pressure is perfect as she scrubs my whole
-back, goshigoshi... goshigoshi, rubbing thoroughly
-over every inch.</t>
+          <t>Nono-chan’s pressure is perfect as she scrubs my
+whole back, goshigoshi... goshigoshi, rubbing
+thoroughly over every inch.</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2799,8 +2802,8 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... it feels really good. Nono-chan, you're a pro
-at washing my back.」</t>
+          <t>「Yeah... it feels really good. Nono-chan, you're a
+pro at washing my back.」</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2998,9 +3001,9 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>Come to think of it, she kept pressing hard on my back
-sometimes, and maybe she was stimulating pressure
-points as well.</t>
+          <t>Come to think of it, she kept pressing hard on my
+back sometimes, and maybe she was stimulating
+pressure points as well.</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3155,8 +3158,8 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>Seeing her wave her hand side to side and gesture, she
-must be really embarrassed.</t>
+          <t>Seeing her wave her hand side to side and gesture,
+she must be really embarrassed.</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3232,8 +3235,8 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>「Ooh! An expert, are you!？! Really, Janitor-sensei can
-do anything, huh~」</t>
+          <t>「Ooh! An expert, are you!？! Really, Janitor-sensei
+can do anything, huh~」</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3248,8 +3251,8 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan again takes my words at face value, her eyes
-sparkling with delight.</t>
+          <t>Nono-chan again takes my words at face value, her
+eyes sparkling with delight.</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3280,9 +3283,9 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>Having her back washed is basically the same as baring
-her skin in front of me, so it's natural she'd be
-embarrassed.</t>
+          <t>Having her back washed is basically the same as
+baring her skin in front of me, so it's natural she'd
+be embarrassed.</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3329,8 +3332,8 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>Trying to come up with an excuse to decline, Nono-chan
-panics and slips her foot.</t>
+          <t>Trying to come up with an excuse to decline,
+Nono-chan panics and slips her foot.</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3496,8 +3499,8 @@
       <c r="B198" s="1" t="inlineStr">
         <is>
           <t>I slipped on the floor, hunched down… and, frantic,
-dove in—somehow I managed to slide into the spot where
-Nono-chan was supposed to have fallen.</t>
+dove in—somehow I managed to slide into the spot
+where Nono-chan was supposed to have fallen.</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3834,8 +3837,8 @@
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan is surprised too, but I'm also startled when
-I remember my own words.</t>
+          <t>Nono-chan is surprised too, but I'm also startled
+when I remember my own words.</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -4278,8 +4281,8 @@
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t>...It's adorable how she desperately tries to cover it
-up.</t>
+          <t>...It's adorable how she desperately tries to cover
+it up.</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4354,8 +4357,8 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>「O-Okay, then I guess it's fine... P-Please... d-do...
-it... …ahh…！」</t>
+          <t>「O-Okay, then I guess it's fine... P-Please...
+d-do... it... …ahh…！」</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4446,8 +4449,9 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>「Auuu... but, but you know？ Naughty things... no！ It's
-not that I don't like them... i-it's just, fwaa...」</t>
+          <t>「Auuu... but, but you know？ Naughty things... no！
+It's not that I don't like them... i-it's just,
+fwaa...」</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4477,8 +4481,8 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>The thing my finger touches is so soft it could become
-a habit... Nono-chan's slit.</t>
+          <t>The thing my finger touches is so soft it could
+become a habit... Nono-chan's slit.</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4891,8 +4895,8 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>Sliding it along without any pressure, her little body
-begins to get sweaty.</t>
+          <t>Sliding it along without any pressure, her little
+body begins to get sweaty.</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -5382,8 +5386,8 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>In her head, she probably knows what's happened to her
-body.</t>
+          <t>In her head, she probably knows what's happened to
+her body.</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5414,8 +5418,8 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t>So while explaining it to me, she is herself trying to
-understand it.</t>
+          <t>So while explaining it to me, she is herself trying
+to understand it.</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5523,8 +5527,8 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>Her hips tremble… and combined with the movement of my
-finger, Nono's breaths turn sweet.</t>
+          <t>Her hips tremble… and combined with the movement of
+my finger, Nono's breaths turn sweet.</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5720,8 +5724,8 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>「If we're going to study... then... together... toge—！
-Togetherrr... study... please...」</t>
+          <t>「If we're going to study... then... together...
+toge—！ Togetherrr... study... please...」</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5783,8 +5787,8 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>「I practiced properly too, nngh！ I studied a lot... so
-please...」</t>
+          <t>「I practiced properly too, nngh！ I studied a lot...
+so please...」</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -5814,8 +5818,8 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>「Nngh, ahh！ No, Nono-chan... hey, ah！ There—it's so...
-good！ Nnngh, hah！」</t>
+          <t>「Nngh, ahh！ No, Nono-chan... hey, ah！ There—it's
+so... good！ Nnngh, hah！」</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -5987,8 +5991,8 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t>「Ha, hah！ Fuu, fuu... my pussy... it feels... weird...
-u！ ...nn, nnh！ Ah！」</t>
+          <t>「Ha, hah！ Fuu, fuu... my pussy... it feels...
+weird... u！ ...nn, nnh！ Ah！」</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -6431,8 +6435,8 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>When that pulsing spot is stroked gently, I just can't
-take it anymore.</t>
+          <t>When that pulsing spot is stroked gently, I just
+can't take it anymore.</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -7359,8 +7363,8 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>Just when I thought the feeling had faded, her fingers
-reached for my glans this time.</t>
+          <t>Just when I thought the feeling had faded, her
+fingers reached for my glans this time.</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7375,8 +7379,8 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>She rubs with two fingers and gently pushes them in...
-and the pleasure rises up immediately！</t>
+          <t>She rubs with two fingers and gently pushes them
+in... and the pleasure rises up immediately！</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -7421,7 +7425,8 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t>Just as the urge to cum swells up, she stops me again.</t>
+          <t>Just as the urge to cum swells up, she stops me
+again.</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -7512,8 +7517,8 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t>「Nn... ufa, fuaa！？ I-—suddenly, haa... no！ That's bad,
-nyaaah！」</t>
+          <t>「Nn... ufa, fuaa！？ I-—suddenly, haa... no！ That's
+bad, nyaaah！」</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7528,8 +7533,8 @@
       </c>
       <c r="B460" s="1" t="inlineStr">
         <is>
-          <t>I return the stimulation Nono-chan gives me right back
-at her.</t>
+          <t>I return the stimulation Nono-chan gives me right
+back at her.</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -7762,8 +7767,8 @@
       </c>
       <c r="B475" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan too... nn, nnah！ You look like you can feel
-really good... right...？」</t>
+          <t>「Nono-chan too... nn, nnah！ You look like you can
+feel really good... right...？」</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -7824,8 +7829,8 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t>「Fufuu, ha, ha... so much is... coming out... it’s...！
-Nnn, aaah！」</t>
+          <t>「Fufuu, ha, ha... so much is... coming out...
+it’s...！ Nnn, aaah！」</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -7932,8 +7937,8 @@
       </c>
       <c r="B486" s="1" t="inlineStr">
         <is>
-          <t>I want to come, I want to come... I'm about to lose my
-mind！</t>
+          <t>I want to come, I want to come... I'm about to lose
+my mind！</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -8181,7 +8186,8 @@
       <c r="B502" s="1" t="inlineStr">
         <is>
           <t>And if it splatters onto her chest... Nono-chan would
-end up looking like she’s completely wrapped in white.</t>
+end up looking like she’s completely wrapped in
+white.</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -8211,8 +8217,8 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>「M-my body... it's so hot...！ Fuuwaa... so much... got
-all over me...」</t>
+          <t>「M-my body... it's so hot...！ Fuuwaa... so much...
+got all over me...」</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -8778,8 +8784,8 @@
       </c>
       <c r="B541" s="1" t="inlineStr">
         <is>
-          <t>What I thought was a yawn from Nono-chan turned into a
-healthy, sleeping breath.</t>
+          <t>What I thought was a yawn from Nono-chan turned into
+a healthy, sleeping breath.</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -8887,8 +8893,8 @@
       <c r="B548" s="1" t="inlineStr">
         <is>
           <t>Even though the horny feeling rose up again, looking
-at Nono-chan's sleeping face made other thoughts cross
-my mind.</t>
+at Nono-chan's sleeping face made other thoughts
+cross my mind.</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -8903,8 +8909,8 @@
       </c>
       <c r="B549" s="1" t="inlineStr">
         <is>
-          <t>Do you remember when I said things like I love you and
-that we seemed like a couple halfway through？</t>
+          <t>Do you remember when I said things like I love you
+and that we seemed like a couple halfway through？</t>
         </is>
       </c>
       <c r="C549" t="n">

--- a/processed_ruby_restored_xlsx/sc111_ノノ１：風呂.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc111_ノノ１：風呂.ss.xlsx
@@ -1500,8 +1500,8 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>「Eh？ No, it's a bath, so I can't put it away, you
-know？」</t>
+          <t>Eh？ No, it's a bath, so I can't put it away, you
+know？</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1531,9 +1531,8 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>「It's obvious you bathe naked, but Nono-chan
-sometimes says things that totally miss the point...
-ahaha！」</t>
+          <t>It's obvious you bathe naked, but Nono-chan sometimes
+says things that totally miss the point... ahaha！</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1563,7 +1562,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>「Uwa... I-I'm sorry...」</t>
+          <t>Uwa... I-I'm sorry...</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1623,7 +1622,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>「But please don't laugh at me...」</t>
+          <t>But please don't laugh at me...</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1653,7 +1652,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, sorry. I won't laugh.」</t>
+          <t>Yeah, sorry. I won't laugh.</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1714,7 +1713,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>「Then, could you wash my back for me？」</t>
+          <t>Then, could you wash my back for me？</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1744,7 +1743,7 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>「Y-Yes... leave it to me！」</t>
+          <t>Y-Yes... leave it to me！</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1820,8 +1819,8 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Nono-chan, how long are you going to keep that
-bath towel on？」</t>
+          <t>Ah... Nono-chan, how long are you going to keep that
+bath towel on？</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1851,7 +1850,7 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>「Eh... this, you mean？」</t>
+          <t>Eh... this, you mean？</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1881,8 +1880,8 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>「Yeah. You should take it off before it gets wet...
-right？」</t>
+          <t>Yeah. You should take it off before it gets wet...
+right？</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1912,7 +1911,7 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>「Well... that's true... okay.」</t>
+          <t>Well... that's true... okay.</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -3019,7 +3018,7 @@
       <c r="B167" s="1" t="inlineStr">
         <is>
           <t>Was that the first place she touched with her
-finger...？</t>
+finger...？"</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3315,9 +3314,9 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>「Ah, but... um... Janitor-sensei does a lot of
+          <t>Ah, but... um... Janitor-sensei does a lot of
 physical work, so don't push yourself too hard...
-kya！」</t>
+kya！</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3438,7 +3437,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>「Haa... haha, thank God... S-Sa---afe...」</t>
+          <t>Haa... haha, thank God... S-Sa---afe...</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3468,7 +3467,7 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei...」</t>
+          <t>Janitor-sensei...</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3715,8 +3714,8 @@
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Uh, um, well... th-thank... you... so... so...
-much」</t>
+          <t>Ah！ Uh, um, well... th-thank... you... so... so...
+much</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3746,7 +3745,7 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>「…I... love you.」</t>
+          <t>…I... love you.</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -4188,8 +4187,8 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>Hmm...？ I speak slowly, thinking over each word, but
-my whole line of thought might be off-target.</t>
+          <t>Hmm...？ He speaks slowly, thinking over each word,
+but his whole line of thought might be off-target.</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4357,8 +4356,8 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>「O-Okay, then I guess it's fine... P-Please...
-d-do... it... …ahh…！」</t>
+          <t>O-Okay, then I guess it's fine... P-Please... d-do...
+it... …ahh…！</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4373,7 +4372,7 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>After she says it, even letting out a sigh is cute.</t>
+          <t>After they say it, even letting out a sigh is cute.</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4388,7 +4387,7 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>Watching her like that, I couldn't hold back the
+          <t>Watching them like that, I couldn't hold back the
 throbbing desire rising up from deep inside me.</t>
         </is>
       </c>
@@ -4419,7 +4418,7 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>「It's fine, leave it to me…okay？」</t>
+          <t>It's fine, leave it to me…okay？</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4926,8 +4925,8 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>「This is supposed to be studying, right？ And Nono...
-are you feeling... horny？」</t>
+          <t>「This is supposed to be studying, right？ And
+Monono... are you feeling... horny？」</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -5370,8 +5369,8 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t>「Hwoaaah... I-I've read it before... y-yes... Ah！
-Haaah！」</t>
+          <t>Hwoaaah... I-I've read it before... y-yes... Ah！
+Haaah！</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5465,8 +5464,8 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>「Mm... I'll stroke you plenty, so tell me what's
-coming out, okay?」</t>
+          <t>Mm... I'll stroke you plenty, so tell me what's
+coming out, okay?</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5664,7 +5663,7 @@
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t>「Ha, haa... u-ugh！ Janitor-sensei too... is...！」</t>
+          <t>Ha, haa... u-ugh！ Janitor-sensei too... is...！</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -6159,7 +6158,7 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t>The thick, gooey love juices cling to my finger.</t>
+          <t>The thick, gooey love juices cling to his finger.</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -6869,8 +6868,8 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>When the area below my penis... her fingers and palm
-stroked my balls, a new kind of stimulation hit...！</t>
+          <t>When the area below his penis... her fingers and palm
+stroked his balls, a new kind of stimulation hit...！</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -6962,7 +6961,7 @@
       <c r="B423" s="1" t="inlineStr">
         <is>
           <t>「Janitor-sensei seems to have a lot built
-up……Mmm！　Looks like it'd be better to loosen me up
+up……Mmm！　Looks like it'd be better to loosen him up
 real good, don't you think？」</t>
         </is>
       </c>
@@ -6978,7 +6977,7 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>Little by little, pressure was applied to my balls,
+          <t>Little by little, pressure was applied to his balls,
 and eventually they were squeezed tight—gyuu~.</t>
         </is>
       </c>
@@ -7009,8 +7008,8 @@
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ahh！ There— that's really... ugh！ It's...
-coming...！」</t>
+          <t>Ah, ahh！ There— that's really... ugh！ It's...
+coming...！</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -7072,8 +7071,8 @@
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t>「Ah, fuu... that looks so good, right...？ Fuu... fuh！
-I'm going to come all at once...」</t>
+          <t>Ah, fuu... that looks so good, right...？ Fuu... fuh！
+I'm going to come all at once...</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -7242,7 +7241,7 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>「Ah, aaahhh... not like that...」</t>
+          <t>Ah, aaahhh... not like that...</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -7550,7 +7549,7 @@
       <c r="B461" s="1" t="inlineStr">
         <is>
           <t>That evens things out, and if I match the way I rub
-her pussy to Nono-chan's hand movements, it's easier
+my pussy to Nono-chan's hand movements, it's easier
 to get the pressure right.</t>
         </is>
       </c>
@@ -8028,7 +8027,7 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>「Ahh, fuh...！ I-I... me too？ Nnngh！ Nnnh！ Ah, haaah！」</t>
+          <t>Ahh, fuh...！ I-I... me too？ Nnngh！ Nnnh！ Ah, haaah！</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8106,8 +8105,8 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>「U-uuuh… aaahh！ Really… just like Nono-chan said… so
-much, haa！」</t>
+          <t>U-uuuh… aaahh！ Really… just like Nono-chan said… so
+much, haa！</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -8137,8 +8136,8 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>「Ha, haa... haha！ Ah, fuu... fufuu, n！ It's coming
-out... a lot... isn't it...！」</t>
+          <t>Ha, haa... haha！ Ah, fuu... fufuu, n！ It's coming
+out... a lot... isn't it...！</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8153,7 +8152,7 @@
       </c>
       <c r="B500" s="1" t="inlineStr">
         <is>
-          <t>Even I'm surprised at myself... it's really an
+          <t>She's even surprised herself... it's really an
 incredible amount.</t>
         </is>
       </c>
